--- a/add-mapping-xds-fhir/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:09:08+00:00</t>
+    <t>2026-09-15T14:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:24:26+00:00</t>
+    <t>2026-09-15T15:11:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:11:37+00:00</t>
+    <t>2026-09-16T10:02:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T10:02:19+00:00</t>
+    <t>2026-09-22T13:51:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T13:51:41+00:00</t>
+    <t>2026-09-22T15:20:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/add-mapping-xds-fhir/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T15:20:18+00:00</t>
+    <t>2026-09-22T17:31:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
     <t>Identifiant unique affecté à la version de la fiche référençant le document.</t>
   </si>
   <si>
-    <t>Les valeurs possibles pour cette métadonnée doivent être un code provenant du jeu de valeurs mis à disposition par le projet. En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J52_AvailabilityStatus_CISIS peut être utilisé.</t>
+    <t>Cet identifiant est attribué par le registre du système cible lors de la soumission. Il change à chaque nouvelle version de la fiche, à la différence de logicalId qui reste invariable.</t>
   </si>
   <si>
     <t>DocumentEntry.logicalId</t>
